--- a/Bases/Metas_Medalhas_Upmat.xlsx
+++ b/Bases/Metas_Medalhas_Upmat.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\djdan\Documents\GitHub\Dash-Upmat\Bases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97161E7A-DE05-4A39-92BE-AA38A065CB52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A8937C0-C064-4D17-B2A8-CD28EAE1E061}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23880" yWindow="510" windowWidth="20730" windowHeight="11040" xr2:uid="{7A3D93D2-1B78-47A2-8F18-8B9569ABF04B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="2" xr2:uid="{7A3D93D2-1B78-47A2-8F18-8B9569ABF04B}"/>
   </bookViews>
   <sheets>
-    <sheet name="Metas_Medalhas" sheetId="1" r:id="rId1"/>
+    <sheet name="Kangaroo_2025" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
+    <sheet name="Kangaroo_2026" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="16">
   <si>
     <t>gold</t>
   </si>
@@ -543,6 +544,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -635,5 +637,102 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F231168-402C-4523-8E0F-781C95807A09}">
+  <dimension ref="A1:M2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2">
+        <v>15234</v>
+      </c>
+      <c r="C2">
+        <v>32125</v>
+      </c>
+      <c r="D2">
+        <v>46815</v>
+      </c>
+      <c r="E2">
+        <v>55824</v>
+      </c>
+      <c r="F2">
+        <v>4297</v>
+      </c>
+      <c r="G2">
+        <v>394</v>
+      </c>
+      <c r="H2">
+        <v>35</v>
+      </c>
+      <c r="I2">
+        <v>143</v>
+      </c>
+      <c r="J2">
+        <v>180</v>
+      </c>
+      <c r="K2">
+        <v>2048</v>
+      </c>
+      <c r="L2">
+        <v>18</v>
+      </c>
+      <c r="M2">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>